--- a/TestData/T2276_T2277_RejectApproveEventExpenseFormAsFirstLevelApprover.xlsx
+++ b/TestData/T2276_T2277_RejectApproveEventExpenseFormAsFirstLevelApprover.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4890CA87-5DC3-45D3-8614-9ED7C77F162F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08AB966A-E475-434C-8ECE-0AB43252D94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExpenseRequest" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
     <t>1000.0</t>
   </si>
   <si>
-    <t>Bingo@123456</t>
+    <t>Bingo@12345</t>
   </si>
 </sst>
 </file>
@@ -793,10 +793,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{B417F8DC-9DC0-418C-877E-78A8508EF3A7}"/>
-    <hyperlink ref="A2" r:id="rId2" tooltip="mailto:kspero@hl.com.test" display="mailto:kspero@hl.com.test" xr:uid="{BF9A316F-3890-4091-A712-BAB45FA8B7A3}"/>
-    <hyperlink ref="A3" r:id="rId3" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{102C98B0-E08F-485E-82F8-4D662884A9CD}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{D92467C4-C6AA-4153-A927-AF0E2ABA33B8}"/>
+    <hyperlink ref="A2" r:id="rId1" tooltip="mailto:kspero@hl.com.test" display="mailto:kspero@hl.com.test" xr:uid="{BF9A316F-3890-4091-A712-BAB45FA8B7A3}"/>
+    <hyperlink ref="A3" r:id="rId2" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{102C98B0-E08F-485E-82F8-4D662884A9CD}"/>
+    <hyperlink ref="B2" r:id="rId3" xr:uid="{64214915-A35B-4574-871B-FAAA59049AD9}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{B090A55E-3667-4BBF-BB44-2B1FFA901F39}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
